--- a/product_selector_out/STM32MP133.xlsx
+++ b/product_selector_out/STM32MP133.xlsx
@@ -61,12 +61,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="BC12" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp133c.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="BC13" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp133a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2538,9 +2538,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -2568,12 +2568,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="K12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="L12" s="8" t="inlineStr">
+      <c r="K12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="L12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -2593,12 +2593,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q12" s="8" t="inlineStr">
+      <c r="P12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -2618,7 +2618,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U12" s="8" t="inlineStr">
+      <c r="U12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -2633,7 +2633,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="X12" s="8" t="inlineStr">
+      <c r="X12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -2668,12 +2668,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF12" s="8" t="inlineStr">
+      <c r="AE12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -2688,7 +2688,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI12" s="8" t="inlineStr">
+      <c r="AI12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -2728,7 +2728,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AQ12" s="8" t="inlineStr">
+      <c r="AQ12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -2753,27 +2753,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AX12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ12" s="8" t="inlineStr">
+      <c r="AV12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AX12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -2788,9 +2788,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -2815,9 +2815,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -2845,12 +2845,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="K13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="L13" s="8" t="inlineStr">
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="L13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -2870,12 +2870,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q13" s="8" t="inlineStr">
+      <c r="P13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -2895,7 +2895,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U13" s="8" t="inlineStr">
+      <c r="U13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -2910,7 +2910,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="X13" s="8" t="inlineStr">
+      <c r="X13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -2945,12 +2945,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF13" s="8" t="inlineStr">
+      <c r="AE13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -2965,7 +2965,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI13" s="8" t="inlineStr">
+      <c r="AI13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3005,7 +3005,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AQ13" s="8" t="inlineStr">
+      <c r="AQ13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3030,27 +3030,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AX13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ13" s="8" t="inlineStr">
+      <c r="AV13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AX13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3065,9 +3065,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -3092,7 +3092,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
@@ -3122,12 +3122,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="K14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="L14" s="8" t="inlineStr">
+      <c r="K14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="L14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3147,12 +3147,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q14" s="8" t="inlineStr">
+      <c r="P14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3172,7 +3172,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U14" s="8" t="inlineStr">
+      <c r="U14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3187,7 +3187,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="X14" s="8" t="inlineStr">
+      <c r="X14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3222,12 +3222,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF14" s="8" t="inlineStr">
+      <c r="AE14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3242,7 +3242,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI14" s="8" t="inlineStr">
+      <c r="AI14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3282,7 +3282,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AQ14" s="8" t="inlineStr">
+      <c r="AQ14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3307,27 +3307,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AX14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ14" s="8" t="inlineStr">
+      <c r="AV14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AX14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3369,7 +3369,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
@@ -3399,12 +3399,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="K15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="L15" s="8" t="inlineStr">
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="L15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3424,12 +3424,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q15" s="8" t="inlineStr">
+      <c r="P15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3449,7 +3449,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U15" s="8" t="inlineStr">
+      <c r="U15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3464,7 +3464,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="X15" s="8" t="inlineStr">
+      <c r="X15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3499,12 +3499,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF15" s="8" t="inlineStr">
+      <c r="AE15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3519,7 +3519,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI15" s="8" t="inlineStr">
+      <c r="AI15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3559,7 +3559,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AQ15" s="8" t="inlineStr">
+      <c r="AQ15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3584,27 +3584,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AX15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ15" s="8" t="inlineStr">
+      <c r="AV15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AX15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>

--- a/product_selector_out/STM32MP133.xlsx
+++ b/product_selector_out/STM32MP133.xlsx
@@ -61,12 +61,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="BC12" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp133c.pdf</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="BC13" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp133a.pdf</t>
         </is>
       </c>
     </row>
@@ -2538,9 +2538,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -2568,12 +2568,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="K12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="L12" s="7" t="inlineStr">
+      <c r="K12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="L12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -2593,12 +2593,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q12" s="7" t="inlineStr">
+      <c r="P12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -2618,7 +2618,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U12" s="7" t="inlineStr">
+      <c r="U12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -2633,7 +2633,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="X12" s="7" t="inlineStr">
+      <c r="X12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -2668,12 +2668,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF12" s="7" t="inlineStr">
+      <c r="AE12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -2688,7 +2688,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI12" s="7" t="inlineStr">
+      <c r="AI12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -2728,7 +2728,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AQ12" s="7" t="inlineStr">
+      <c r="AQ12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -2753,27 +2753,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AX12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ12" s="7" t="inlineStr">
+      <c r="AV12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AX12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -2788,9 +2788,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -2815,9 +2815,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -2845,12 +2845,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="K13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="L13" s="7" t="inlineStr">
+      <c r="K13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="L13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -2870,12 +2870,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q13" s="7" t="inlineStr">
+      <c r="P13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -2895,7 +2895,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U13" s="7" t="inlineStr">
+      <c r="U13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -2910,7 +2910,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="X13" s="7" t="inlineStr">
+      <c r="X13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -2945,12 +2945,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF13" s="7" t="inlineStr">
+      <c r="AE13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -2965,7 +2965,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI13" s="7" t="inlineStr">
+      <c r="AI13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3005,7 +3005,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AQ13" s="7" t="inlineStr">
+      <c r="AQ13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3030,27 +3030,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AX13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ13" s="7" t="inlineStr">
+      <c r="AV13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AX13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3065,9 +3065,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -3092,7 +3092,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
@@ -3122,12 +3122,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="K14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="L14" s="7" t="inlineStr">
+      <c r="K14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="L14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3147,12 +3147,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q14" s="7" t="inlineStr">
+      <c r="P14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3172,7 +3172,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U14" s="7" t="inlineStr">
+      <c r="U14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3187,7 +3187,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="X14" s="7" t="inlineStr">
+      <c r="X14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3222,12 +3222,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF14" s="7" t="inlineStr">
+      <c r="AE14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3242,7 +3242,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI14" s="7" t="inlineStr">
+      <c r="AI14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3282,7 +3282,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AQ14" s="7" t="inlineStr">
+      <c r="AQ14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3307,27 +3307,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AX14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ14" s="7" t="inlineStr">
+      <c r="AV14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AX14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3369,7 +3369,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
@@ -3399,12 +3399,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="K15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="L15" s="7" t="inlineStr">
+      <c r="K15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="L15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3424,12 +3424,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q15" s="7" t="inlineStr">
+      <c r="P15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3449,7 +3449,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U15" s="7" t="inlineStr">
+      <c r="U15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3464,7 +3464,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="X15" s="7" t="inlineStr">
+      <c r="X15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3499,12 +3499,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF15" s="7" t="inlineStr">
+      <c r="AE15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3519,7 +3519,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI15" s="7" t="inlineStr">
+      <c r="AI15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3559,7 +3559,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AQ15" s="7" t="inlineStr">
+      <c r="AQ15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3584,27 +3584,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AX15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ15" s="7" t="inlineStr">
+      <c r="AV15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AX15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>

--- a/product_selector_out/STM32MP133.xlsx
+++ b/product_selector_out/STM32MP133.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC15"/>
+  <dimension ref="A1:BD15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.828125" customWidth="1" min="1" max="1"/>
@@ -551,7 +551,8 @@
     <col width="18" customWidth="1" min="52" max="52"/>
     <col width="18" customWidth="1" min="53" max="53"/>
     <col width="18" customWidth="1" min="54" max="54"/>
-    <col width="52" customWidth="1" min="55" max="55"/>
+    <col width="18" customWidth="1" min="55" max="55"/>
+    <col width="52" customWidth="1" min="56" max="56"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -833,6 +834,11 @@
         </is>
       </c>
       <c r="BC10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BD10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -910,6 +916,7 @@
       <c r="BA11" s="2" t="n"/>
       <c r="BB11" s="2" t="n"/>
       <c r="BC11" s="2" t="n"/>
+      <c r="BD11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1187,6 +1194,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD12" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -1464,6 +1476,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -1738,6 +1755,11 @@
       </c>
       <c r="BC14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BD14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32mp133c.pdf</t>
         </is>
       </c>
@@ -2015,12 +2037,17 @@
       </c>
       <c r="BC15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BD15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32mp133a.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="55">
+  <mergeCells count="56">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -2033,16 +2060,18 @@
     <mergeCell ref="V10:V11"/>
     <mergeCell ref="G10:G11"/>
     <mergeCell ref="M10:M11"/>
+    <mergeCell ref="A9:BD9"/>
+    <mergeCell ref="A1:BD8"/>
+    <mergeCell ref="Y10:Y11"/>
     <mergeCell ref="AJ10:AJ11"/>
-    <mergeCell ref="Y10:Y11"/>
+    <mergeCell ref="Q10:Q11"/>
     <mergeCell ref="AP10:AP11"/>
-    <mergeCell ref="BA10:BA11"/>
-    <mergeCell ref="Q10:Q11"/>
     <mergeCell ref="AR10:AR11"/>
+    <mergeCell ref="S10:S11"/>
     <mergeCell ref="AT10:AT11"/>
-    <mergeCell ref="S10:S11"/>
     <mergeCell ref="AV10:AV11"/>
     <mergeCell ref="BB10:BB11"/>
+    <mergeCell ref="BD10:BD11"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="AK10:AK11"/>
@@ -2054,9 +2083,8 @@
     <mergeCell ref="Z10:Z11"/>
     <mergeCell ref="AQ10:AQ11"/>
     <mergeCell ref="AW10:AW11"/>
-    <mergeCell ref="A1:BC8"/>
     <mergeCell ref="AY10:AY11"/>
-    <mergeCell ref="A9:BC9"/>
+    <mergeCell ref="BA10:BA11"/>
     <mergeCell ref="AE10:AF10"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="I10:I11"/>
@@ -2094,7 +2122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC15"/>
+  <dimension ref="A1:BD15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2152,6 +2180,7 @@
     <col width="16" customWidth="1" min="53" max="53"/>
     <col width="16" customWidth="1" min="54" max="54"/>
     <col width="16" customWidth="1" min="55" max="55"/>
+    <col width="16" customWidth="1" min="56" max="56"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2439,6 +2468,11 @@
         </is>
       </c>
       <c r="BC10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BD10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -2516,6 +2550,7 @@
       <c r="BA11" s="2" t="n"/>
       <c r="BB11" s="2" t="n"/>
       <c r="BC11" s="2" t="n"/>
+      <c r="BD11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -2793,6 +2828,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -3070,6 +3110,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -3342,7 +3387,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC14" s="6" t="inlineStr">
+      <c r="BC14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -3619,7 +3669,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC15" s="6" t="inlineStr">
+      <c r="BC15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -3627,8 +3682,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BC9"/>
-    <mergeCell ref="A1:BC8"/>
+    <mergeCell ref="A9:BD9"/>
+    <mergeCell ref="A1:BD8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
